--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_attribute_type_info[生物属性信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_attribute_type_info[生物属性信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureAttributeTypeInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -92,7 +92,7 @@
     <t>#2980B9</t>
   </si>
   <si>
-    <t>魔法</t>
+    <t>魔力</t>
   </si>
   <si>
     <t>Slime</t>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>复活CD</t>
+  </si>
+  <si>
+    <t>#00F7FF</t>
+  </si>
+  <si>
+    <t>魔力回复</t>
   </si>
 </sst>
 </file>
@@ -177,7 +183,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +201,12 @@
       <sz val="10.5"/>
       <color rgb="FF6A9955"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF6A9955"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -655,64 +667,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
@@ -721,10 +733,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
@@ -733,10 +745,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
@@ -745,10 +757,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
@@ -757,10 +769,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
@@ -769,10 +781,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
@@ -781,11 +793,11 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -793,6 +805,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1383,6 +1401,20 @@
         <v>45</v>
       </c>
     </row>
+    <row r="13" ht="14.25" spans="1:6">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="20" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_attribute_type_info[生物属性信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_attribute_type_info[生物属性信息].xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="17.375" customWidth="1" style="5" min="1" max="1"/>
@@ -1420,20 +1420,38 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>#E74C3C</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>暴击伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>#40E0D0</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>魔力回复</t>
         </is>
       </c>
     </row>
